--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/109.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/109.xlsx
@@ -426,13 +426,13 @@
         <v>-41.06411070495884</v>
       </c>
       <c r="E2">
-        <v>-10.50859503159512</v>
+        <v>-11.24769221253895</v>
       </c>
       <c r="F2">
-        <v>0.4806061943457234</v>
+        <v>1.081218949949922</v>
       </c>
       <c r="G2">
-        <v>-18.48943101955854</v>
+        <v>-22.99762888175483</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-40.9696313760924</v>
       </c>
       <c r="E3">
-        <v>-10.49656733159841</v>
+        <v>-12.17807384747042</v>
       </c>
       <c r="F3">
-        <v>-0.1983941402179893</v>
+        <v>1.615472849650657</v>
       </c>
       <c r="G3">
-        <v>-18.52568512432303</v>
+        <v>-22.37417328310476</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-40.64221904606737</v>
       </c>
       <c r="E4">
-        <v>-11.11196526644356</v>
+        <v>-13.07959897011698</v>
       </c>
       <c r="F4">
-        <v>0.5420569733875992</v>
+        <v>1.077070485996702</v>
       </c>
       <c r="G4">
-        <v>-17.50274056788843</v>
+        <v>-22.0741680533369</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-40.02711582116063</v>
       </c>
       <c r="E5">
-        <v>-11.13467087275639</v>
+        <v>-13.41565191125415</v>
       </c>
       <c r="F5">
-        <v>0.4234032833454036</v>
+        <v>1.849317653991347</v>
       </c>
       <c r="G5">
-        <v>-17.45006096352895</v>
+        <v>-21.78195459080121</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-39.21859922203961</v>
       </c>
       <c r="E6">
-        <v>-13.55304844830213</v>
+        <v>-14.52135720905193</v>
       </c>
       <c r="F6">
-        <v>0.2650699663417089</v>
+        <v>2.117813066791139</v>
       </c>
       <c r="G6">
-        <v>-17.31620808834257</v>
+        <v>-21.32351240940476</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-38.20129396980226</v>
       </c>
       <c r="E7">
-        <v>-13.10655331161511</v>
+        <v>-16.0233536250422</v>
       </c>
       <c r="F7">
-        <v>0.931248001877488</v>
+        <v>1.755160444784738</v>
       </c>
       <c r="G7">
-        <v>-17.47015194852986</v>
+        <v>-20.91284032716419</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-37.06600867080772</v>
       </c>
       <c r="E8">
-        <v>-13.83676262032382</v>
+        <v>-15.57044593006965</v>
       </c>
       <c r="F8">
-        <v>0.9383355133758406</v>
+        <v>2.131292261169492</v>
       </c>
       <c r="G8">
-        <v>-16.04709120292272</v>
+        <v>-19.86896934745953</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-35.79280297805467</v>
       </c>
       <c r="E9">
-        <v>-14.35207231545192</v>
+        <v>-16.74994133347565</v>
       </c>
       <c r="F9">
-        <v>0.66874582723695</v>
+        <v>2.039326912110691</v>
       </c>
       <c r="G9">
-        <v>-16.85880694135182</v>
+        <v>-19.18430810530154</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-34.45983394905071</v>
       </c>
       <c r="E10">
-        <v>-14.24356966959077</v>
+        <v>-17.94862457320237</v>
       </c>
       <c r="F10">
-        <v>1.083773635020155</v>
+        <v>2.240949881217285</v>
       </c>
       <c r="G10">
-        <v>-15.01412791411972</v>
+        <v>-18.09547749299331</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-33.03934664970313</v>
       </c>
       <c r="E11">
-        <v>-16.42015558822764</v>
+        <v>-18.24752288582763</v>
       </c>
       <c r="F11">
-        <v>0.9752309974965306</v>
+        <v>2.620570781102632</v>
       </c>
       <c r="G11">
-        <v>-14.27569577636317</v>
+        <v>-17.56648972931423</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-31.60390828763895</v>
       </c>
       <c r="E12">
-        <v>-16.77851127417915</v>
+        <v>-18.62301056849405</v>
       </c>
       <c r="F12">
-        <v>1.605151391811775</v>
+        <v>2.56642703092085</v>
       </c>
       <c r="G12">
-        <v>-15.04095462016571</v>
+        <v>-16.75622817562239</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-30.12998710598787</v>
       </c>
       <c r="E13">
-        <v>-17.3628639543712</v>
+        <v>-19.50406866573185</v>
       </c>
       <c r="F13">
-        <v>1.500076300236269</v>
+        <v>2.659296957183509</v>
       </c>
       <c r="G13">
-        <v>-12.19571686599551</v>
+        <v>-15.37609459795462</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-28.69344049292362</v>
       </c>
       <c r="E14">
-        <v>-17.39486860084033</v>
+        <v>-21.60246207475618</v>
       </c>
       <c r="F14">
-        <v>1.887367882271539</v>
+        <v>2.907396307791572</v>
       </c>
       <c r="G14">
-        <v>-11.34289234323474</v>
+        <v>-14.05875334382002</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-27.27499108305544</v>
       </c>
       <c r="E15">
-        <v>-18.75335079950115</v>
+        <v>-22.04018562912515</v>
       </c>
       <c r="F15">
-        <v>1.948214781476774</v>
+        <v>3.190914991808536</v>
       </c>
       <c r="G15">
-        <v>-11.97557496595595</v>
+        <v>-13.40966610746055</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-25.93689608808729</v>
       </c>
       <c r="E16">
-        <v>-20.60701207799862</v>
+        <v>-22.29753936886815</v>
       </c>
       <c r="F16">
-        <v>1.711803694922212</v>
+        <v>2.923382141930797</v>
       </c>
       <c r="G16">
-        <v>-9.945841140616563</v>
+        <v>-12.35385358199613</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-24.64678270026742</v>
       </c>
       <c r="E17">
-        <v>-22.11802096256377</v>
+        <v>-23.47186817738607</v>
       </c>
       <c r="F17">
-        <v>1.614851574098558</v>
+        <v>3.388825218215783</v>
       </c>
       <c r="G17">
-        <v>-9.737602930540186</v>
+        <v>-11.45002555290337</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-23.44452519698367</v>
       </c>
       <c r="E18">
-        <v>-23.04852719383498</v>
+        <v>-24.34551694562038</v>
       </c>
       <c r="F18">
-        <v>2.831569212474111</v>
+        <v>3.104400300260156</v>
       </c>
       <c r="G18">
-        <v>-9.020097216053705</v>
+        <v>-11.26106638626007</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-22.28947423092222</v>
       </c>
       <c r="E19">
-        <v>-23.54086132391413</v>
+        <v>-25.18860223171528</v>
       </c>
       <c r="F19">
-        <v>2.334732668357829</v>
+        <v>3.582524024747197</v>
       </c>
       <c r="G19">
-        <v>-9.107760797934105</v>
+        <v>-10.12955271063173</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-21.21179367763227</v>
       </c>
       <c r="E20">
-        <v>-23.56157754200237</v>
+        <v>-26.18385287432924</v>
       </c>
       <c r="F20">
-        <v>1.737574204823304</v>
+        <v>3.638912650590565</v>
       </c>
       <c r="G20">
-        <v>-7.047528254281332</v>
+        <v>-9.704728434648887</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-20.17589190898821</v>
       </c>
       <c r="E21">
-        <v>-24.60349366706211</v>
+        <v>-27.1470697979948</v>
       </c>
       <c r="F21">
-        <v>1.882457320307743</v>
+        <v>3.575401721817927</v>
       </c>
       <c r="G21">
-        <v>-8.569729414991411</v>
+        <v>-8.774091974722282</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-19.21322729774156</v>
       </c>
       <c r="E22">
-        <v>-24.15031601335344</v>
+        <v>-27.19841594960366</v>
       </c>
       <c r="F22">
-        <v>2.14041092953951</v>
+        <v>3.489099092324663</v>
       </c>
       <c r="G22">
-        <v>-7.049645568144725</v>
+        <v>-7.993398408897084</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-18.30041583034946</v>
       </c>
       <c r="E23">
-        <v>-25.34825582825301</v>
+        <v>-28.07294519863883</v>
       </c>
       <c r="F23">
-        <v>2.08490368661272</v>
+        <v>3.466970085526277</v>
       </c>
       <c r="G23">
-        <v>-7.49062643702967</v>
+        <v>-8.609261309590048</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-17.47395080732137</v>
       </c>
       <c r="E24">
-        <v>-25.3727930007601</v>
+        <v>-27.34698877832675</v>
       </c>
       <c r="F24">
-        <v>2.363836528687786</v>
+        <v>3.347333951744361</v>
       </c>
       <c r="G24">
-        <v>-7.316098161113747</v>
+        <v>-7.831258116065994</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-16.71995317438535</v>
       </c>
       <c r="E25">
-        <v>-26.36530252389968</v>
+        <v>-28.3797989875568</v>
       </c>
       <c r="F25">
-        <v>2.122241518926505</v>
+        <v>3.319328506590516</v>
       </c>
       <c r="G25">
-        <v>-6.986277575429224</v>
+        <v>-7.458626540576395</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-16.07610546071729</v>
       </c>
       <c r="E26">
-        <v>-24.43738182691427</v>
+        <v>-28.45025614107685</v>
       </c>
       <c r="F26">
-        <v>2.114640419638417</v>
+        <v>3.196630726887853</v>
       </c>
       <c r="G26">
-        <v>-7.487543147667566</v>
+        <v>-7.8762634366999</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-15.53430132868214</v>
       </c>
       <c r="E27">
-        <v>-25.69209604062424</v>
+        <v>-28.31573570287132</v>
       </c>
       <c r="F27">
-        <v>2.112489977860749</v>
+        <v>2.742375580745077</v>
       </c>
       <c r="G27">
-        <v>-6.112343877277007</v>
+        <v>-8.200286864019857</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-15.13049808772114</v>
       </c>
       <c r="E28">
-        <v>-24.91150412533404</v>
+        <v>-27.65663560186066</v>
       </c>
       <c r="F28">
-        <v>1.670552654997602</v>
+        <v>2.560068482736962</v>
       </c>
       <c r="G28">
-        <v>-6.522254274783112</v>
+        <v>-7.609608511025067</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-14.85620809807428</v>
       </c>
       <c r="E29">
-        <v>-23.25956016767217</v>
+        <v>-28.0057794650937</v>
       </c>
       <c r="F29">
-        <v>1.200359720024963</v>
+        <v>2.174100631811366</v>
       </c>
       <c r="G29">
-        <v>-8.199952688712195</v>
+        <v>-7.444290942026591</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-14.73903044043856</v>
       </c>
       <c r="E30">
-        <v>-24.34651371633834</v>
+        <v>-27.15170062862198</v>
       </c>
       <c r="F30">
-        <v>2.293024369626874</v>
+        <v>2.26155137852491</v>
       </c>
       <c r="G30">
-        <v>-6.954969526292593</v>
+        <v>-7.279192675573769</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-14.76434669451436</v>
       </c>
       <c r="E31">
-        <v>-23.26895888490025</v>
+        <v>-27.15027192392624</v>
       </c>
       <c r="F31">
-        <v>1.839463395367644</v>
+        <v>2.228105216269476</v>
       </c>
       <c r="G31">
-        <v>-6.530303200357515</v>
+        <v>-7.299817557843564</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-14.94968715232028</v>
       </c>
       <c r="E32">
-        <v>-24.54296476521406</v>
+        <v>-26.48249784106369</v>
       </c>
       <c r="F32">
-        <v>2.169426982924771</v>
+        <v>1.922485689945821</v>
       </c>
       <c r="G32">
-        <v>-6.798293521890702</v>
+        <v>-8.187149597237374</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-15.27373534592344</v>
       </c>
       <c r="E33">
-        <v>-21.88034098486648</v>
+        <v>-26.10891648239536</v>
       </c>
       <c r="F33">
-        <v>2.103720880534714</v>
+        <v>2.137019593392449</v>
       </c>
       <c r="G33">
-        <v>-8.129995176648723</v>
+        <v>-8.263421195094454</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-15.74298359390188</v>
       </c>
       <c r="E34">
-        <v>-24.56496017239035</v>
+        <v>-25.03129519957607</v>
       </c>
       <c r="F34">
-        <v>1.203527396973269</v>
+        <v>2.602015351279923</v>
       </c>
       <c r="G34">
-        <v>-7.037424672713724</v>
+        <v>-7.745835858417062</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-16.32740236281858</v>
       </c>
       <c r="E35">
-        <v>-23.8145704098543</v>
+        <v>-25.06968748506279</v>
       </c>
       <c r="F35">
-        <v>1.799895598005522</v>
+        <v>2.060766717229948</v>
       </c>
       <c r="G35">
-        <v>-7.422640037132489</v>
+        <v>-8.066535807872532</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-17.02178291013351</v>
       </c>
       <c r="E36">
-        <v>-23.18762239431481</v>
+        <v>-23.85081133187476</v>
       </c>
       <c r="F36">
-        <v>1.739093430640039</v>
+        <v>2.421762604430751</v>
       </c>
       <c r="G36">
-        <v>-7.763150316545326</v>
+        <v>-8.776519967192018</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-17.78939714957609</v>
       </c>
       <c r="E37">
-        <v>-21.08999317617426</v>
+        <v>-23.40932496804548</v>
       </c>
       <c r="F37">
-        <v>2.196638852106735</v>
+        <v>2.867253623451908</v>
       </c>
       <c r="G37">
-        <v>-7.654587724213062</v>
+        <v>-9.354170704677152</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-18.61783470351885</v>
       </c>
       <c r="E38">
-        <v>-19.88254666055215</v>
+        <v>-22.57647734786629</v>
       </c>
       <c r="F38">
-        <v>1.922537048724795</v>
+        <v>2.620347121903876</v>
       </c>
       <c r="G38">
-        <v>-6.874354954808197</v>
+        <v>-8.940318082838465</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-19.46927121492499</v>
       </c>
       <c r="E39">
-        <v>-20.77966937919439</v>
+        <v>-22.08168866989417</v>
       </c>
       <c r="F39">
-        <v>1.912459130902336</v>
+        <v>2.816290804096877</v>
       </c>
       <c r="G39">
-        <v>-7.370164070851112</v>
+        <v>-9.127646839484616</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-20.33015757411028</v>
       </c>
       <c r="E40">
-        <v>-19.73497475575835</v>
+        <v>-21.59992861584803</v>
       </c>
       <c r="F40">
-        <v>2.012081908232616</v>
+        <v>3.039323757096227</v>
       </c>
       <c r="G40">
-        <v>-8.828381103122187</v>
+        <v>-9.56294933888389</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-21.16718859454186</v>
       </c>
       <c r="E41">
-        <v>-18.35798584743409</v>
+        <v>-20.98768296839843</v>
       </c>
       <c r="F41">
-        <v>2.621481985245711</v>
+        <v>3.216473439654512</v>
       </c>
       <c r="G41">
-        <v>-8.691615942344422</v>
+        <v>-10.56644906960388</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-21.97116356681688</v>
       </c>
       <c r="E42">
-        <v>-17.56074370794266</v>
+        <v>-21.15228303962403</v>
       </c>
       <c r="F42">
-        <v>2.946364367154066</v>
+        <v>3.376946429659638</v>
       </c>
       <c r="G42">
-        <v>-8.922442314623112</v>
+        <v>-10.09628790842406</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-22.71844241113122</v>
       </c>
       <c r="E43">
-        <v>-17.35146338928455</v>
+        <v>-19.02109587397887</v>
       </c>
       <c r="F43">
-        <v>2.762846196003058</v>
+        <v>3.44345604843041</v>
       </c>
       <c r="G43">
-        <v>-9.840307012009992</v>
+        <v>-10.71909669510168</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-23.40710782589537</v>
       </c>
       <c r="E44">
-        <v>-16.74417667615679</v>
+        <v>-20.26352488859</v>
       </c>
       <c r="F44">
-        <v>2.758439281420165</v>
+        <v>3.627280715520454</v>
       </c>
       <c r="G44">
-        <v>-9.665045116863967</v>
+        <v>-11.03819364737821</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-24.02314500878335</v>
       </c>
       <c r="E45">
-        <v>-15.78723525480305</v>
+        <v>-18.02513918543968</v>
       </c>
       <c r="F45">
-        <v>2.463729353791379</v>
+        <v>3.69402227716401</v>
       </c>
       <c r="G45">
-        <v>-7.991895925384899</v>
+        <v>-11.11416500960731</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-24.57016248590331</v>
       </c>
       <c r="E46">
-        <v>-17.2362366942885</v>
+        <v>-17.41415611423283</v>
       </c>
       <c r="F46">
-        <v>2.387531149877464</v>
+        <v>3.964401397437769</v>
       </c>
       <c r="G46">
-        <v>-9.433906760606638</v>
+        <v>-11.94538431550432</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-25.0416790484317</v>
       </c>
       <c r="E47">
-        <v>-14.81575344060108</v>
+        <v>-17.36412653061395</v>
       </c>
       <c r="F47">
-        <v>2.05367754899679</v>
+        <v>4.422657558136066</v>
       </c>
       <c r="G47">
-        <v>-10.41095312175717</v>
+        <v>-12.61987018061844</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-25.44478380721756</v>
       </c>
       <c r="E48">
-        <v>-15.21234774322028</v>
+        <v>-16.86672132950718</v>
       </c>
       <c r="F48">
-        <v>2.617476000485773</v>
+        <v>3.943915871566537</v>
       </c>
       <c r="G48">
-        <v>-10.24464477518637</v>
+        <v>-12.3774834312903</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-25.77797693583424</v>
       </c>
       <c r="E49">
-        <v>-13.3375258530228</v>
+        <v>-16.28003039133925</v>
       </c>
       <c r="F49">
-        <v>2.843684914107456</v>
+        <v>4.397934104632113</v>
       </c>
       <c r="G49">
-        <v>-10.02043533507385</v>
+        <v>-12.50801674472907</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-26.04906641152685</v>
       </c>
       <c r="E50">
-        <v>-12.73110716106194</v>
+        <v>-15.735004469182</v>
       </c>
       <c r="F50">
-        <v>2.269762156221458</v>
+        <v>4.226382528981946</v>
       </c>
       <c r="G50">
-        <v>-10.17121366744442</v>
+        <v>-12.78934536037826</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-26.25990005382913</v>
       </c>
       <c r="E51">
-        <v>-13.71123180803088</v>
+        <v>-15.07034944802439</v>
       </c>
       <c r="F51">
-        <v>2.764594051222965</v>
+        <v>3.740074534555246</v>
       </c>
       <c r="G51">
-        <v>-11.08377985868363</v>
+        <v>-12.87423372075831</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-26.41725334527141</v>
       </c>
       <c r="E52">
-        <v>-13.41630811864348</v>
+        <v>-14.60525623102479</v>
       </c>
       <c r="F52">
-        <v>2.715717060988183</v>
+        <v>3.91897538580305</v>
       </c>
       <c r="G52">
-        <v>-10.78038000826118</v>
+        <v>-13.2455455648571</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-26.52469738755301</v>
       </c>
       <c r="E53">
-        <v>-12.2330374461432</v>
+        <v>-13.48669674417667</v>
       </c>
       <c r="F53">
-        <v>2.306642729728897</v>
+        <v>3.824640905972242</v>
       </c>
       <c r="G53">
-        <v>-10.79112974911509</v>
+        <v>-13.50221047635404</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-26.58633363035305</v>
       </c>
       <c r="E54">
-        <v>-10.74315594758746</v>
+        <v>-13.74473161057694</v>
       </c>
       <c r="F54">
-        <v>2.806892147544713</v>
+        <v>3.976036645977491</v>
       </c>
       <c r="G54">
-        <v>-11.19496755470226</v>
+        <v>-13.57327494412414</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-26.60615669428177</v>
       </c>
       <c r="E55">
-        <v>-10.81997374425149</v>
+        <v>-13.25732734234037</v>
       </c>
       <c r="F55">
-        <v>2.418003473156846</v>
+        <v>3.712241389821183</v>
       </c>
       <c r="G55">
-        <v>-11.21062288464287</v>
+        <v>-13.75073769696048</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-26.58427913335292</v>
       </c>
       <c r="E56">
-        <v>-10.87248279503129</v>
+        <v>-11.60099759351947</v>
       </c>
       <c r="F56">
-        <v>2.410425568156036</v>
+        <v>3.913503190740156</v>
       </c>
       <c r="G56">
-        <v>-11.68371591199851</v>
+        <v>-14.16189472500884</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-26.52419699553401</v>
       </c>
       <c r="E57">
-        <v>-11.9103952243739</v>
+        <v>-12.53250474871996</v>
       </c>
       <c r="F57">
-        <v>3.253923929935078</v>
+        <v>3.725364386216333</v>
       </c>
       <c r="G57">
-        <v>-10.96502883558455</v>
+        <v>-13.69523065620882</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-26.42174303331353</v>
       </c>
       <c r="E58">
-        <v>-11.50608840832449</v>
+        <v>-11.97903119472801</v>
       </c>
       <c r="F58">
-        <v>2.591992105706049</v>
+        <v>3.740281626405946</v>
       </c>
       <c r="G58">
-        <v>-11.24402475094158</v>
+        <v>-13.92564453084211</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-26.28078040286031</v>
       </c>
       <c r="E59">
-        <v>-10.75007935086595</v>
+        <v>-11.36986307687011</v>
       </c>
       <c r="F59">
-        <v>2.439519488077161</v>
+        <v>3.589561834201382</v>
       </c>
       <c r="G59">
-        <v>-12.5337456326745</v>
+        <v>-14.2486902343127</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-26.09481776086271</v>
       </c>
       <c r="E60">
-        <v>-9.926763350677238</v>
+        <v>-10.65772854384706</v>
       </c>
       <c r="F60">
-        <v>3.244909635857814</v>
+        <v>4.082541499690229</v>
       </c>
       <c r="G60">
-        <v>-13.20343947609162</v>
+        <v>-13.93831708508737</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-25.87087563971603</v>
       </c>
       <c r="E61">
-        <v>-10.10170907131299</v>
+        <v>-10.30298615174816</v>
       </c>
       <c r="F61">
-        <v>2.352784450799636</v>
+        <v>3.778762605735594</v>
       </c>
       <c r="G61">
-        <v>-12.53328744699875</v>
+        <v>-14.22610207211038</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-25.60260745746176</v>
       </c>
       <c r="E62">
-        <v>-9.87680021843955</v>
+        <v>-11.31995808959097</v>
       </c>
       <c r="F62">
-        <v>3.029829009925339</v>
+        <v>3.536862756770083</v>
       </c>
       <c r="G62">
-        <v>-12.59613329079603</v>
+        <v>-13.89821735354017</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-25.30225869189987</v>
       </c>
       <c r="E63">
-        <v>-8.699871499632287</v>
+        <v>-10.10607824962671</v>
       </c>
       <c r="F63">
-        <v>2.58032537920502</v>
+        <v>3.473843878234707</v>
       </c>
       <c r="G63">
-        <v>-12.35128460931847</v>
+        <v>-14.41542804836874</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-24.96704997440269</v>
       </c>
       <c r="E64">
-        <v>-8.0364749015061</v>
+        <v>-10.61664497742186</v>
       </c>
       <c r="F64">
-        <v>1.875530512085534</v>
+        <v>3.658082729026151</v>
       </c>
       <c r="G64">
-        <v>-11.4843894785839</v>
+        <v>-13.94764266476683</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-24.61760974400893</v>
       </c>
       <c r="E65">
-        <v>-7.291671208201947</v>
+        <v>-9.670896460588525</v>
       </c>
       <c r="F65">
-        <v>2.440503588551687</v>
+        <v>3.87920381005984</v>
       </c>
       <c r="G65">
-        <v>-12.27472452418408</v>
+        <v>-13.62266501029882</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-24.25485613054404</v>
       </c>
       <c r="E66">
-        <v>-8.036246474883233</v>
+        <v>-9.609491231150935</v>
       </c>
       <c r="F66">
-        <v>2.098477314874993</v>
+        <v>3.717938900817638</v>
       </c>
       <c r="G66">
-        <v>-12.57204917194301</v>
+        <v>-13.90067798031729</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-23.90440693760429</v>
       </c>
       <c r="E67">
-        <v>-9.282450758588636</v>
+        <v>-10.1263832997938</v>
       </c>
       <c r="F67">
-        <v>1.938420165306073</v>
+        <v>3.264276865735266</v>
       </c>
       <c r="G67">
-        <v>-12.62104893180132</v>
+        <v>-13.20516517826635</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-23.56617141672304</v>
       </c>
       <c r="E68">
-        <v>-8.678262341109205</v>
+        <v>-9.295483535725948</v>
       </c>
       <c r="F68">
-        <v>2.058054642353183</v>
+        <v>3.417564596888509</v>
       </c>
       <c r="G68">
-        <v>-12.48168869089999</v>
+        <v>-14.00400341899979</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-23.26641221399758</v>
       </c>
       <c r="E69">
-        <v>-7.80877093741105</v>
+        <v>-10.2570267152276</v>
       </c>
       <c r="F69">
-        <v>2.225181079337594</v>
+        <v>3.719408424590204</v>
       </c>
       <c r="G69">
-        <v>-11.14431780426237</v>
+        <v>-13.4924972011028</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-22.99914590096533</v>
       </c>
       <c r="E70">
-        <v>-9.324032710372819</v>
+        <v>-10.23599069986735</v>
       </c>
       <c r="F70">
-        <v>2.676152577095673</v>
+        <v>3.240497751070504</v>
       </c>
       <c r="G70">
-        <v>-11.06569523090099</v>
+        <v>-12.74904199075295</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-22.78465357576194</v>
       </c>
       <c r="E71">
-        <v>-9.08494894724774</v>
+        <v>-10.191721620356</v>
       </c>
       <c r="F71">
-        <v>2.630443263809196</v>
+        <v>3.405283221774603</v>
       </c>
       <c r="G71">
-        <v>-11.16164531611359</v>
+        <v>-13.06079622386697</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-22.60600175372505</v>
       </c>
       <c r="E72">
-        <v>-8.042260324881585</v>
+        <v>-10.43156957436485</v>
       </c>
       <c r="F72">
-        <v>2.396063334126298</v>
+        <v>3.25062537093713</v>
       </c>
       <c r="G72">
-        <v>-11.38483395509098</v>
+        <v>-12.50829478902803</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-22.47695496533909</v>
       </c>
       <c r="E73">
-        <v>-9.625439562638277</v>
+        <v>-10.59483646475518</v>
       </c>
       <c r="F73">
-        <v>1.928874059356211</v>
+        <v>3.47675641802295</v>
       </c>
       <c r="G73">
-        <v>-13.13444663415457</v>
+        <v>-12.1426939487223</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-22.37319073903472</v>
       </c>
       <c r="E74">
-        <v>-9.68530810388568</v>
+        <v>-11.19461001859632</v>
       </c>
       <c r="F74">
-        <v>1.801787589153516</v>
+        <v>3.321611487152631</v>
       </c>
       <c r="G74">
-        <v>-10.60405031857739</v>
+        <v>-11.73555877271654</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-22.30496232420974</v>
       </c>
       <c r="E75">
-        <v>-9.822837543696052</v>
+        <v>-11.32098808599953</v>
       </c>
       <c r="F75">
-        <v>2.109106925387716</v>
+        <v>3.128631703526847</v>
       </c>
       <c r="G75">
-        <v>-11.20201395435368</v>
+        <v>-11.61864310306501</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-22.24276767535753</v>
       </c>
       <c r="E76">
-        <v>-10.51146490062057</v>
+        <v>-11.18413146642378</v>
       </c>
       <c r="F76">
-        <v>2.789884108030434</v>
+        <v>3.084559244228302</v>
       </c>
       <c r="G76">
-        <v>-11.26701366243863</v>
+        <v>-11.27206023173325</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-22.19466416584129</v>
       </c>
       <c r="E77">
-        <v>-9.939202218595099</v>
+        <v>-11.17473690240702</v>
       </c>
       <c r="F77">
-        <v>2.364852107123619</v>
+        <v>2.83214906965607</v>
       </c>
       <c r="G77">
-        <v>-10.14179057590257</v>
+        <v>-11.33066361556997</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-22.12748943431189</v>
       </c>
       <c r="E78">
-        <v>-11.14903267751765</v>
+        <v>-12.19082420623764</v>
       </c>
       <c r="F78">
-        <v>2.410220133040142</v>
+        <v>2.951414094841532</v>
       </c>
       <c r="G78">
-        <v>-11.17294853482081</v>
+        <v>-10.22367658000284</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-22.04958323120616</v>
       </c>
       <c r="E79">
-        <v>-9.831355780123276</v>
+        <v>-12.22194837190591</v>
       </c>
       <c r="F79">
-        <v>1.891773140119627</v>
+        <v>2.811275867840328</v>
       </c>
       <c r="G79">
-        <v>-9.660251789794682</v>
+        <v>-9.904118831305983</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-21.92892086869656</v>
       </c>
       <c r="E80">
-        <v>-10.81560871914909</v>
+        <v>-13.2523144162713</v>
       </c>
       <c r="F80">
-        <v>2.428474037128232</v>
+        <v>3.063053169716822</v>
       </c>
       <c r="G80">
-        <v>-11.1778293218339</v>
+        <v>-10.51341048786311</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-21.77933625298983</v>
       </c>
       <c r="E81">
-        <v>-12.77198722013223</v>
+        <v>-14.39351721126238</v>
       </c>
       <c r="F81">
-        <v>2.461971558162638</v>
+        <v>3.158522512889464</v>
       </c>
       <c r="G81">
-        <v>-9.437706699359003</v>
+        <v>-9.274592598795428</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-21.57339835023902</v>
       </c>
       <c r="E82">
-        <v>-12.28405964726872</v>
+        <v>-14.17133701822936</v>
       </c>
       <c r="F82">
-        <v>2.687232819475519</v>
+        <v>2.990754919535286</v>
       </c>
       <c r="G82">
-        <v>-9.869035645490602</v>
+        <v>-9.421777241236326</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-21.33199612644834</v>
       </c>
       <c r="E83">
-        <v>-12.97416139421355</v>
+        <v>-15.8228241226455</v>
       </c>
       <c r="F83">
-        <v>1.613976818121201</v>
+        <v>3.007988274983127</v>
       </c>
       <c r="G83">
-        <v>-9.484031751383718</v>
+        <v>-9.555169320002372</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-21.03367625880611</v>
       </c>
       <c r="E84">
-        <v>-17.33210527129952</v>
+        <v>-16.55052489171401</v>
       </c>
       <c r="F84">
-        <v>1.962292057119949</v>
+        <v>2.777046070021847</v>
       </c>
       <c r="G84">
-        <v>-9.323100233298312</v>
+        <v>-8.44337459827071</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-20.70905038456334</v>
       </c>
       <c r="E85">
-        <v>-17.00863656047657</v>
+        <v>-17.43050730721868</v>
       </c>
       <c r="F85">
-        <v>1.403549960257654</v>
+        <v>3.067248022244598</v>
       </c>
       <c r="G85">
-        <v>-8.681764297629856</v>
+        <v>-8.11597678356674</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-20.34421454438303</v>
       </c>
       <c r="E86">
-        <v>-16.8535930285094</v>
+        <v>-17.9011907466615</v>
       </c>
       <c r="F86">
-        <v>1.850591683056852</v>
+        <v>2.989659817828785</v>
       </c>
       <c r="G86">
-        <v>-9.238710525135167</v>
+        <v>-8.658584801777657</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-19.97948138808324</v>
       </c>
       <c r="E87">
-        <v>-18.54102202373061</v>
+        <v>-19.63111955336968</v>
       </c>
       <c r="F87">
-        <v>1.661130804158161</v>
+        <v>2.654596800540024</v>
       </c>
       <c r="G87">
-        <v>-8.334604451743454</v>
+        <v>-8.024004167738706</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-19.60645278460871</v>
       </c>
       <c r="E88">
-        <v>-20.61550124194657</v>
+        <v>-20.60187870880113</v>
       </c>
       <c r="F88">
-        <v>1.768909686936404</v>
+        <v>2.495381272252348</v>
       </c>
       <c r="G88">
-        <v>-8.92880339381936</v>
+        <v>-7.243790978918273</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-19.27190244760478</v>
       </c>
       <c r="E89">
-        <v>-19.93271745335608</v>
+        <v>-20.73567025841916</v>
       </c>
       <c r="F89">
-        <v>2.043536675251719</v>
+        <v>2.670478260386496</v>
       </c>
       <c r="G89">
-        <v>-7.863955081325097</v>
+        <v>-7.586529528839626</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-18.96744217463256</v>
       </c>
       <c r="E90">
-        <v>-23.22774656892398</v>
+        <v>-23.37295944968528</v>
       </c>
       <c r="F90">
-        <v>1.568111771762998</v>
+        <v>2.653403951479993</v>
       </c>
       <c r="G90">
-        <v>-7.623138694868512</v>
+        <v>-6.424659420478116</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-18.7380228361358</v>
       </c>
       <c r="E91">
-        <v>-24.43077406769646</v>
+        <v>-24.94083825692131</v>
       </c>
       <c r="F91">
-        <v>1.694449397833562</v>
+        <v>2.435117543698684</v>
       </c>
       <c r="G91">
-        <v>-7.543963949026114</v>
+        <v>-6.674476348912564</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-18.56527633050457</v>
       </c>
       <c r="E92">
-        <v>-25.28959171828981</v>
+        <v>-27.58655016075418</v>
       </c>
       <c r="F92">
-        <v>1.411286911799801</v>
+        <v>2.6854518295595</v>
       </c>
       <c r="G92">
-        <v>-7.499899801817304</v>
+        <v>-6.132376120524619</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-18.48176554805271</v>
       </c>
       <c r="E93">
-        <v>-26.61222339679471</v>
+        <v>-27.96850024024204</v>
       </c>
       <c r="F93">
-        <v>2.06870910388799</v>
+        <v>2.276604470968582</v>
       </c>
       <c r="G93">
-        <v>-7.24359517307394</v>
+        <v>-6.294579071225896</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-18.45192660707966</v>
       </c>
       <c r="E94">
-        <v>-30.33156950057504</v>
+        <v>-30.27109043726288</v>
       </c>
       <c r="F94">
-        <v>1.672433049001957</v>
+        <v>2.542551825637363</v>
       </c>
       <c r="G94">
-        <v>-7.889379817525653</v>
+        <v>-6.114338486144617</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-18.49247872327965</v>
       </c>
       <c r="E95">
-        <v>-30.9821659013981</v>
+        <v>-32.46317198735269</v>
       </c>
       <c r="F95">
-        <v>1.798038398288446</v>
+        <v>2.031420973618373</v>
       </c>
       <c r="G95">
-        <v>-8.465981035685161</v>
+        <v>-6.238946714733864</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-18.55532060972741</v>
       </c>
       <c r="E96">
-        <v>-36.55336456014394</v>
+        <v>-34.57760717511916</v>
       </c>
       <c r="F96">
-        <v>1.039797266340335</v>
+        <v>2.252709384867428</v>
       </c>
       <c r="G96">
-        <v>-5.797561180437295</v>
+        <v>-6.444947516695657</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-18.64645161214816</v>
       </c>
       <c r="E97">
-        <v>-36.46720826781603</v>
+        <v>-36.95455023788274</v>
       </c>
       <c r="F97">
-        <v>0.9209878432264134</v>
+        <v>1.679103063329298</v>
       </c>
       <c r="G97">
-        <v>-6.941673004090053</v>
+        <v>-6.458656536543593</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-18.71554908759263</v>
       </c>
       <c r="E98">
-        <v>-38.27310346286666</v>
+        <v>-38.42013129697691</v>
       </c>
       <c r="F98">
-        <v>1.147062561328843</v>
+        <v>1.58868013437451</v>
       </c>
       <c r="G98">
-        <v>-7.842647489344726</v>
+        <v>-6.660224294189677</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-18.76772054057702</v>
       </c>
       <c r="E99">
-        <v>-42.52229965462331</v>
+        <v>-40.9494806025164</v>
       </c>
       <c r="F99">
-        <v>0.6714015731303251</v>
+        <v>1.487982136155397</v>
       </c>
       <c r="G99">
-        <v>-8.165703635793674</v>
+        <v>-6.580586141182357</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-18.76445862528196</v>
       </c>
       <c r="E100">
-        <v>-42.88853398245801</v>
+        <v>-44.27929909274673</v>
       </c>
       <c r="F100">
-        <v>0.6575703226057817</v>
+        <v>0.9537663413551898</v>
       </c>
       <c r="G100">
-        <v>-7.381103090687876</v>
+        <v>-6.425761154695565</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-18.71959185566902</v>
       </c>
       <c r="E101">
-        <v>-45.23752800961117</v>
+        <v>-45.22436855952845</v>
       </c>
       <c r="F101">
-        <v>0.4425551376981281</v>
+        <v>0.8946209087953051</v>
       </c>
       <c r="G101">
-        <v>-7.705681301233445</v>
+        <v>-6.478422483842912</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-18.62022486991677</v>
       </c>
       <c r="E102">
-        <v>-48.05431899433638</v>
+        <v>-48.00953180171226</v>
       </c>
       <c r="F102">
-        <v>0.1101975683469105</v>
+        <v>0.5635025770786756</v>
       </c>
       <c r="G102">
-        <v>-7.991354195882243</v>
+        <v>-7.052895945160661</v>
       </c>
     </row>
   </sheetData>
